--- a/docs/programme-template.xlsx
+++ b/docs/programme-template.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Programme" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Courses" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="How to fill" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Credit scheme" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="How to fill" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -475,8 +476,15 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Degree</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Institution and Programme are required. Source: the URL or document the syllabus came from.</t>
         </is>
@@ -553,7 +561,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Credits</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -587,75 +637,89 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Credit scheme (optional, for the regulatory checklist): the credits a student earns, one row per category and semester, from the programme's regulations - e.g. I | Major | 8. Use the university's own category names (Major, Minor, AEC, SEC, VAC, ...).</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Degree (Programme sheet, optional): e.g. 3-year or 4-year (Honours); it decides which credit minimums apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Semester</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Topics</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>MTH101</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Calculus</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Limits and continuity
 Differentiation and its applications
 Riemann integration</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Evaluate limits and derivatives; Apply integration to areas and volumes</t>
         </is>

--- a/docs/programme-template.xlsx
+++ b/docs/programme-template.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Programme" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Courses" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Credit scheme" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="How to fill" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Programme outcomes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="How to fill" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -603,7 +604,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -651,75 +688,82 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Programme outcomes (optional, for CO-PO mapping): the programme's own POs and PSOs, one per row - e.g. PSO1 | Problem solving | Apply mathematical methods to solve problems in science. Without them, course outcomes are mapped to UGC's LOCF graduate attributes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Semester</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Topics</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>MTH101</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Calculus</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Limits and continuity
 Differentiation and its applications
 Riemann integration</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Evaluate limits and derivatives; Apply integration to areas and volumes</t>
         </is>

--- a/docs/programme-template.xlsx
+++ b/docs/programme-template.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Programme" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Courses" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Credit scheme" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Programme outcomes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="How to fill" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Courses" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit scheme" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme outcomes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to fill" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
